--- a/fichas/ficha_3_reuniones.xlsx
+++ b/fichas/ficha_3_reuniones.xlsx
@@ -578,7 +578,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Periodo de corte</t>
@@ -586,7 +586,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Datos acumulados hasta el cierre del I bimestre o I trimestre. El mismo corte se usa para el PRE 2026 y para el histórico 2024–2025, para que el modelo no aprenda de la ausencia de quien ya desertó.</t>
+          <t>Datos acumulados hasta el cierre del I bimestre. El mismo corte se usa para el PRE 2026 y para el histórico 2024–2025, para que el modelo no aprenda de la ausencia de quien ya desertó.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,11 @@
           <t>Periodo de corte</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n"/>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>I bimestre</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4315,8 +4319,8 @@
       <formula1>2024</formula1>
       <formula2>2026</formula2>
     </dataValidation>
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elija I bimestre o I trimestre." type="list">
-      <formula1>"I bimestre,I trimestre"</formula1>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="El corte es el I bimestre." type="list">
+      <formula1>"I bimestre"</formula1>
     </dataValidation>
     <dataValidation sqref="A10:A159" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Use el formato EST-001 (sin nombres ni DNI)." type="custom">
       <formula1>AND(LEN(A10)=7,LEFT(A10,4)="EST-",ISNUMBER(VALUE(RIGHT(A10,3))))</formula1>
